--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.940001795148861</v>
+        <v>1.61525029171169</v>
       </c>
       <c r="D2" t="n">
-        <v>8.411123841315161</v>
+        <v>1.366807624213714</v>
       </c>
       <c r="E2" t="n">
-        <v>11.3221234350067</v>
+        <v>1.839845058188588</v>
       </c>
       <c r="F2" t="n">
-        <v>2.677347750038347</v>
+        <v>0.4350690093812314</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.56081767229508</v>
+        <v>2.203632871747951</v>
       </c>
       <c r="D3" t="n">
-        <v>12.64656153352026</v>
+        <v>2.055066249197042</v>
       </c>
       <c r="E3" t="n">
-        <v>11.3221234350067</v>
+        <v>1.839845058188588</v>
       </c>
       <c r="F3" t="n">
-        <v>2.677347750038347</v>
+        <v>0.4350690093812314</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.98537428755924</v>
+        <v>2.597623321728376</v>
       </c>
       <c r="D4" t="n">
-        <v>15.51398493074407</v>
+        <v>2.521022551245911</v>
       </c>
       <c r="E4" t="n">
-        <v>11.3221234350067</v>
+        <v>1.839845058188588</v>
       </c>
       <c r="F4" t="n">
-        <v>2.677347750038347</v>
+        <v>0.4350690093812314</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.64580327760223</v>
+        <v>1.729943032610363</v>
       </c>
       <c r="D5" t="n">
-        <v>9.742021305239765</v>
+        <v>1.583078462101462</v>
       </c>
       <c r="E5" t="n">
-        <v>11.3221234350067</v>
+        <v>1.839845058188588</v>
       </c>
       <c r="F5" t="n">
-        <v>2.677347750038347</v>
+        <v>0.4350690093812314</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.31995543455202</v>
+        <v>6.551992758114704</v>
       </c>
       <c r="D6" t="n">
-        <v>8.884162315238301</v>
+        <v>1.443676376226224</v>
       </c>
       <c r="E6" t="n">
-        <v>11.3221234350067</v>
+        <v>1.839845058188588</v>
       </c>
       <c r="F6" t="n">
-        <v>2.677347750038347</v>
+        <v>0.4350690093812314</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
